--- a/光伏配储项目/电价数据/2026/归湖站.xlsx
+++ b/光伏配储项目/电价数据/2026/归湖站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.33976</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.78388</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.36427</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.38725</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.32683</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.32384</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.32122</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.33379</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.27706</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.36419</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07779000000000001</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.14108</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.29193</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17557</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.27412</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25683</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.2614</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24612</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.9718</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.5483</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.3897</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.60893</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.5908</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.75679</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.14004</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39722</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.70848</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43601</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44308</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.67562</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.90679</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.54902</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.21453</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.40857</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.08793</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.09976</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.3223</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.4058</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.46669</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.72648</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.78023</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.26454</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.83299</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.8663</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79555</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.74303</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.49875</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.46446</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4579</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.40873</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.41819</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7163099999999999</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.68349</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.89625</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.88447</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5066700000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.49897</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.49936</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48236</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39793</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46471</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37359</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.31334</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.28485</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.3774</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.37324</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.4902</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.38195</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30341</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.36396</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.5258400000000001</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.52866</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.68322</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.6448700000000001</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.89597</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.37188</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.36639</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.29883</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.7576900000000001</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.53783</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.44608</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.38458</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.39336</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.4139</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.7091799999999999</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.40474</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.11166</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6601699999999999</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.9177799999999999</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.05063</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.3131</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.19289</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.96353</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.31023</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.17507</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.37093</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.06733</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.1597</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.77147</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.06828</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.99112</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.02938</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.90101</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.1288</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.9647899999999999</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.47128</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.9019400000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.91886</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.46912</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.44477</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.46289</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37804</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33446</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5147</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.49321</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.49203</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37418</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44243</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41183</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36657</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.3815</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36224</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42566</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44079</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.3941</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.33358</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37338</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.3901</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.46964</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44252</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.4359</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39586</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.15236</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.19068</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27629</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.3883</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.11083</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.91384</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.7360800000000001</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.72281</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.92864</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.9245399999999999</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.93984</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.9190700000000001</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.4902</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.8345199999999999</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.8326</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.83958</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.05176</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.58035</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.64998</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.9033600000000001</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.8887200000000001</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.73882</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.7972100000000001</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.55238</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.96078</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.5340199999999999</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.41302</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45736</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.51578</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.53089</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.64211</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.6907300000000001</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.67453</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.6631699999999999</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.61543</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.66255</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.70043</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.48626</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5156900000000001</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.6605599999999999</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.85717</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.79703</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.05112</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.47743</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.65838</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.47899</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.5884400000000001</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.71885</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.90571</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.63152</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.0877</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.81899</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.63748</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.5759</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.71489</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.45297</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.47531</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40727</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34198</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5071600000000001</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.48758</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.43508</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38844</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38814</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.38698</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.3662</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38619</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38425</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36187</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44291</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36414</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38417</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38573</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37457</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.40482</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.4258</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44715</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.44114</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37316</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.52361</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.36155</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.74221</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.47347</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.4621</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37286</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.28623</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.74263</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.42072</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.45477</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.7475000000000001</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.6067899999999999</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.48332</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.56072</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.37261</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.39029</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.8773200000000001</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.63347</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.62536</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45067</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.51819</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.41639</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.5496799999999999</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.6490199999999999</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.79799</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.57413</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.66103</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.61258</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.5841799999999999</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50258</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.51297</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.48338</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.46958</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.45956</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.38631</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.40216</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.3541</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.37137</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37416</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35407</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32759</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31189</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31327</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30991</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.29955</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.34215</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28835</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14319</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.30858</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.3016</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.30346</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.40925</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.44629</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.26846</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25816</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.24256</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.10786</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.29336</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.0356</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26343</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30047</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36395</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.44436</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36561</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42265</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.3512</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31625</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.41669</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.29743</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.23496</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.24214</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.25567</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.3734</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.28576</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32656</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.18743</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.17997</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.24569</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.35785</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.19192</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.24588</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.21142</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.18898</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.16988</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.24658</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.26829</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.19716</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26572</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.09617000000000001</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.03953</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.009890000000000001</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20596</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04914</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27506</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19451</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.008369999999999999</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06011</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05831</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.3152</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.42974</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32741</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.42578</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38983</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.44418</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.48337</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.44925</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7879400000000001</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88748</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8702799999999999</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.65146</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5713400000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44997</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.4198</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32741</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39257</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35305</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.3776600000000001</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38671</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39721</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37404</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3252</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.31252</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44347</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36259</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.31942</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.46103</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.58392</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.63098</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.9448300000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.53747</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.28573</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.4356</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.42813</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.7123700000000001</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.95309</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29147</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26487</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.41023</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.7235900000000001</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.5695</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30314</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28428</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29296</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30763</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29422</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30516</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.17558</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.26106</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26055</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27553</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.25974</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.2798</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29044</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.30947</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30737</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.29966</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.29194</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.29931</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.29952</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.30405</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.29935</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.30247</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.28779</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32269</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.8393999999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30627</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.30885</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.31563</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30595</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.30887</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29171</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.30571</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29548</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.30223</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.2963</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29616</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.29557</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.29523</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.30119</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29134</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29499</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30613</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30314</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30323</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.35336</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.3692</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.56833</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.46226</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.4651</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.23091</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.38732</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.34657</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.38355</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.37252</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.50748</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.5786699999999999</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.45456</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.41854</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.44099</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.43502</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.44844</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.5721900000000001</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.46612</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.4343399999999999</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.46381</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.46727</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.36444</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.36299</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.35355</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.37665</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.37401</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.36816</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.36475</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.50281</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.38818</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.5338099999999999</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.38627</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.34457</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.20292</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.57776</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.64938</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.9362200000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.8901399999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.88585</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.52613</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5770299999999999</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.41767</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.38098</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.45925</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.43204</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.38059</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.43187</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.46836</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.40298</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.37631</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.30228</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.30753</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.4045</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.38892</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.30445</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.42099</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.38249</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.30315</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.40919</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.54689</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33226</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.22376</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.37041</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30466</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30847</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.42503</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.31468</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.45945</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.37724</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.28536</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.32118</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.1701</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.29911</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.2913</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.01116</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.34308</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.3137799999999999</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.37314</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.31445</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.37197</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.41926</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.39392</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.37567</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.36895</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.37496</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37645</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36407</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.36161</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.47171</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.3742799999999999</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.5490700000000001</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.4032</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.35215</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.30293</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.30712</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.30832</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.2905</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.28982</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.19336</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30398</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.20935</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.18313</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.20406</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.18041</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.1719</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.26484</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.2884</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.28596</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.22365</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.21851</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.37186</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.39106</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.32224</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.27009</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.18153</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.26794</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.25537</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.20259</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.17833</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.30371</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.21543</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.36246</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.20688</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.24618</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.30901</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29775</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.32384</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.29382</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28524</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.30287</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26835</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.28486</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.30688</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.27532</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.30147</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.30668</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.28778</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.30268</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.29999</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.29056</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.28989</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.29067</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.29294</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.29984</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.27899</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.27877</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.29775</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30108</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.30335</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.29037</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.30105</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.30111</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.30222</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.30064</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.29971</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.40381</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.41146</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39551</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.38584</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.37748</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.28216</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.28456</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.24638</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.27935</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.30365</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30345</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.30245</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.29665</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.29854</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.29944</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.30192</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30514</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30258</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30388</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.30185</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.29558</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29436</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29411</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.29785</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29389</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29289</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29289</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.29897</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.29353</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.29852</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.29827</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.29999</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.28952</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.30018</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29369</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.30634</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30673</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28179</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.29923</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30282</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28457</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31326</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.2845</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.37439</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30392</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.2864</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.28042</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30123</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.27257</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29424</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28744</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.28703</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.2866</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.28946</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31697</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.38265</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36242</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.31345</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.37158</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.44424</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31327</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.28515</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30254</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.29161</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30247</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.2851</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.29077</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.2845299999999999</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.29061</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.29193</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29597</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.29781</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29248</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29391</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30752</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.29193</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.3088399999999999</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30434</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29288</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29411</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.28645</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.30677</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.30785</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29405</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30257</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.40491</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.09357</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.41747</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.66661</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.49233</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.48653</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.37983</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.43956</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.5002</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.38699</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.4317</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.38714</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.55692</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27648</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.30299</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.43824</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.27557</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.42908</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.7613799999999999</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.55257</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.45354</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.43798</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.41648</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.40169</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.5445399999999999</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.41973</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.43476</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.45873</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.39252</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.45476</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.49862</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.43019</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.56987</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.37754</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.8418</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.47982</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.42721</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.55737</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.54522</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7885800000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.39106</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.28365</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.39736</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34354</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5013299999999999</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.29542</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28278</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.25725</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38327</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.28731</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.27789</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.27871</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.27758</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.19392</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.18636</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.27514</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.27494</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27258</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.27498</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.2751</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27231</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.18811</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29433</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.1855</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.14819</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.23247</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.28908</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.26014</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.18523</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.19098</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.27833</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.19747</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.16084</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.15249</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.22632</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.2448</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.30468</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.36464</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.39357</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31468</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29524</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.31202</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.30426</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.30541</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.30567</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.30782</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.40018</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.40626</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.29809</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.25651</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28481</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.27441</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.28929</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.27095</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.30052</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.28603</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.24173</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.2758</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.27698</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.21246</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.23067</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.31951</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.29095</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.27849</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31533</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.02871</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31611</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.28711</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28339</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.2716</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.30866</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.30912</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28382</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.28034</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29346</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.28117</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.30868</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.28146</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28362</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27085</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.2824700000000001</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.28777</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.28726</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30541</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.27845</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27233</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28192</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.2913</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.27212</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28295</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.26919</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.2902</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.29857</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30603</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31611</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31105</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30561</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31773</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30183</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.31963</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6000800000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.5201</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.19895</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3087</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29515</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.38024</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.28121</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.30647</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32097</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30722</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.40091</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31257</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.41005</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.38853</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.35532</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.44244</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.49336</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.63025</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.59115</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6374299999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.78407</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.38953</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.36276</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48695</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40627</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.4382799999999999</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.31334</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.31276</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.31611</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.30692</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.30638</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.30672</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.28363</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.30021</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.29141</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.27652</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.29212</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.28695</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.30279</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44735</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.40327</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.41971</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.44597</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.47943</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.51918</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.57353</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40364</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.42871</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37706</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35197</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34396</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.41649</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.70357</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40604</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.84138</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39471</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.4933</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.41419</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.3420899999999999</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.32737</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.40423</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.70241</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.5688799999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.64155</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.31611</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.31093</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40356</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.3935</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38522</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.26002</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.28324</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.28731</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.30545</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32609</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.01508</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.27251</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.28128</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.27211</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.27938</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.28895</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.45794</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.36852</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.46293</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.46612</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.37215</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.48739</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.5500499999999999</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.39767</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.38692</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.41558</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.39994</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.44164</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.44222</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.4346</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.34355</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.34308</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.32384</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.31439</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38008</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.33358</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.48904</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38657</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37717</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.44546</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.29685</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.30595</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.36661</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.30785</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.22817</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.26424</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.25384</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.24442</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.28774</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.20971</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.30961</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.30613</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.24221</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.28117</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.2229</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.16056</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.01658</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.26496</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.01896</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.01833</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.1608</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.03035</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.19503</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.15959</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.0185</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.15048</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.15487</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.19099</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.15259</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.15522</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.15785</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.01881</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.16048</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.0189</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.04489</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.17104</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.17718</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.1432</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28245</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30868</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.16613</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.29758</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.21295</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.42146</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>-0.00095</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.38821</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.30099</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.31611</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29189</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30152</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.24653</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.21394</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.29894</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.24065</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.31561</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.26174</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.25906</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.19763</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.2036</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.26188</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.18934</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.20287</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.28848</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.22551</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.31465</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.2851</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.28143</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.27056</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.03062</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.17957</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.17668</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26367</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.03239</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.19587</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.21773</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.20909</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.01522</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.04473</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.03014</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.03015</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.03036</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.03036</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.03024</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.19045</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.0448</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.03036</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.03035</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.16805</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.04474</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30297</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.02962</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.0249</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24284</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.01436</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.008699999999999999</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00039</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.20983</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02208</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.00728</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04298</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.0409</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02937</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04348</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.01632</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.29276</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0492</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.02793</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.02952</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03168</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.2353</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.2858</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.29842</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.02961</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.31427</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.30867</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.27895</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29344</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30437</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29024</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31824</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.3013</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28926</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.31003</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29742</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.26465</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.30191</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.01728</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.27014</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.27467</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.27315</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.15847</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.15821</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.15572</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.15194</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.14138</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.02704</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.02611</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.02461</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41321</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.18144</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27176</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.22639</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.2749</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85619</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.86256</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.35783</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.08866</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.02866</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.24468</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28209</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.5652200000000001</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.30265</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29483</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00264</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29396</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00188</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06947</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.3028</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30916</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30842</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25452</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47546</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.62326</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.50619</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.40759</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.7504400000000001</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.9071399999999999</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.58485</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.41544</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.77408</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.7723099999999999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.77613</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.8654500000000001</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.41062</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34668</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.30395</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.30379</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.29963</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.45665</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.29579</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.28281</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.26196</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.25668</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.17935</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.25382</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.24802</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.24165</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.20783</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.24324</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.19372</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.15663</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.18945</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.15139</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.15396</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.14485</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.17069</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.22252</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.30209</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.26901</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.23257</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.24128</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29616</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.24789</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.27184</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35343</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.31384</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37726</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.28156</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30868</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.2587</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30254</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33499</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.3791600000000001</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33426</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33797</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39606</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.30647</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.31359</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.30334</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.29217</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.28651</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.28756</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.29915</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.29893</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29111</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.29504</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.29731</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.29738</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.29892</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30403</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.30941</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.31591</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.29601</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.55749</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.29893</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.42327</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33407</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.36128</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29557</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.45391</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.41837</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.46346</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.16952</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.7785700000000001</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.7806799999999999</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40626</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.41518</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.52539</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.6521699999999999</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.8208300000000001</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.40596</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.5329299999999999</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.35757</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42222</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.19799</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.31636</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.30461</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31355</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31659</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.3884</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.30944</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30233</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.29674</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.2947</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29046</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.28941</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.30264</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31298</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39095</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43457</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35332</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37537</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39179</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.49113</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.49833</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.99426</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.7744</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.52974</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.66865</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.46162</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.54479</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49434</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.4188</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.6446799999999999</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.60598</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.9406100000000001</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.7894800000000001</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.68371</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.56829</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.3999</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.31817</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28248</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.28022</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.29192</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.28569</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.29635</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.28736</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.30014</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.29789</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.29883</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.2849100000000001</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.27967</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31264</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.28595</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.27685</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30167</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30013</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.30319</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.37173</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.26378</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.42423</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.38103</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.5395700000000001</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.19825</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.37708</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32678</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29657</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43456</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.50726</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.30257</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.3702</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.45277</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.46886</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.6102300000000001</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.58423</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.64378</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.42663</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.39312</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.52996</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.38574</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.45815</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.40169</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.41238</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.30569</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.32193</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.6773400000000001</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.39569</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.44394</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.41926</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.40885</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33609</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33224</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35621</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.3083399999999999</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.3819</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.27082</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.38917</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.4608</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30312</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32428</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35437</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.70913</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.52119</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.60002</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.7537200000000001</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.40413</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.4045</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.38069</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.40887</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5137699999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.53062</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38751</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.39354</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.38383</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.42153</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.49433</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.41337</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.43742</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.40451</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39329</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33384</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33606</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.45639</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36559</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.30133</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37216</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35423</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34474</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30458</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.3083399999999999</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17613</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30446</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29583</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31182</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14579</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19871</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14694</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28727</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04811</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.1219</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22648</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26015</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14317</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.1457</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28352</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18732</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30919</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.2269</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.30904</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.18319</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30889</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.19558</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.2235</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.18921</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.39207</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.4069</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.36766</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.40701</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.64244</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.7309099999999999</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.52546</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>1.17334</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.5707100000000001</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.62701</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.44496</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.43942</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.50166</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.42444</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.35748</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.7090599999999999</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.57885</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.71458</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>1.02569</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.7584500000000001</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.42806</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.69698</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.4275</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.6676299999999999</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.69533</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.5995499999999999</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.4479</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.43753</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.39405</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.42174</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37291</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36673</v>
       </c>
     </row>
   </sheetData>
